--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.14918697791648</v>
+        <v>4.086742883911428</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22816714424935</v>
+        <v>4.09957716094052</v>
       </c>
       <c r="E2" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F2" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.76916889162528</v>
+        <v>4.024989944889108</v>
       </c>
       <c r="D3" t="n">
-        <v>24.85166255461756</v>
+        <v>4.038395165125354</v>
       </c>
       <c r="E3" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F3" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.63644536795034</v>
+        <v>5.953422372291931</v>
       </c>
       <c r="D4" t="n">
-        <v>36.64706552018372</v>
+        <v>5.955148147029855</v>
       </c>
       <c r="E4" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F4" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.20764485090135</v>
+        <v>5.55874228827147</v>
       </c>
       <c r="D5" t="n">
-        <v>34.21338942038395</v>
+        <v>5.559675780812392</v>
       </c>
       <c r="E5" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F5" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.14019389819013</v>
+        <v>5.547781508455897</v>
       </c>
       <c r="D6" t="n">
-        <v>34.12709881536064</v>
+        <v>5.545653557496104</v>
       </c>
       <c r="E6" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F6" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.61502912294803</v>
+        <v>3.024942232479055</v>
       </c>
       <c r="D7" t="n">
-        <v>18.54532542388066</v>
+        <v>3.013615381380607</v>
       </c>
       <c r="E7" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F7" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.46024131654896</v>
+        <v>4.624789213939206</v>
       </c>
       <c r="D8" t="n">
-        <v>28.40614902474166</v>
+        <v>4.61599921652052</v>
       </c>
       <c r="E8" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F8" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.45731204909442</v>
+        <v>6.086813207977843</v>
       </c>
       <c r="D9" t="n">
-        <v>37.37921052925439</v>
+        <v>6.074121711003838</v>
       </c>
       <c r="E9" t="n">
-        <v>6.298213227305598</v>
+        <v>1.02345964943716</v>
       </c>
       <c r="F9" t="n">
-        <v>6.288901242801039</v>
+        <v>1.021946451955169</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
